--- a/Claude outputs/netaim-activities-template.xlsx
+++ b/Claude outputs/netaim-activities-template.xlsx
@@ -42,19 +42,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -65,60 +69,80 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">כותרת באנגלית</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">סוג</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">תאריך</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">שעת התחלה</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">שעת סיום</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">כותרת משנה</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">כותרת משנה באנגלית</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">תיאור</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">תיאור באנגלית</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">מיקום / קומה</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">מסלול</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">מסלול באנגלית</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">שפה</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="O1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">מקומות</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="P1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">רשימת המתנה</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="Q1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">מוצג בעמוד הבית</t>
         </is>
@@ -132,45 +156,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Opening remarks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t xml:space="preserve">מליאה</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">09:00</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">09:30</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">פתיחת הכנס</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The conference opens</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">אולם מרכזי</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">עברית</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">לא</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">כן</t>
         </is>
@@ -184,50 +218,65 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">AI in public service</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t xml:space="preserve">הרצאה</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">09:45</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">10:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">מבט מהשטח</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t xml:space="preserve">A view from the field</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">אולם מרכזי</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">טכנולוגיה</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technology</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">עברית</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve">לא</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">כן</t>
         </is>
@@ -239,57 +288,57 @@
           <t xml:space="preserve">סדנת כתיבה לרשת</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">סדנה</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">11:00</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">12:30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">סדנה מעשית, נדרשת הרשמה</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">חדר 204</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">תוכן</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">עברית</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve">כן</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">לא</t>
         </is>
@@ -303,30 +352,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lunch</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t xml:space="preserve">הפסקה</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">12:30</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">13:30</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve">לא</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">לא</t>
         </is>
@@ -370,157 +424,217 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">סוג</t>
+          <t xml:space="preserve">כותרת באנגלית</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">חובה. אחד מהערכים: הרצאה, סדנה, מליאה, סיור, הפסקה (או talk / workshop / keynote / tour / break).</t>
+          <t xml:space="preserve">לא חובה. אם יישאר ריק — האתר יציג באנגלית את הכותרת העברית.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">תאריך</t>
+          <t xml:space="preserve">סוג</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">תאריך הפעילות, בצורה 2026-10-12.</t>
+          <t xml:space="preserve">חובה. אחד מהערכים: הרצאה, סדנה, מליאה, סיור, הפסקה (או talk / workshop / keynote / tour / break).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">שעת התחלה</t>
+          <t xml:space="preserve">תאריך</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">שעה בצורה 09:00.</t>
+          <t xml:space="preserve">תאריך הפעילות, בצורה 2026-10-12.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">שעת סיום</t>
+          <t xml:space="preserve">שעת התחלה</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">שעה בצורה 09:45. חייבת להיות אחרי שעת ההתחלה.</t>
+          <t xml:space="preserve">שעה בצורה 09:00.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">כותרת משנה</t>
+          <t xml:space="preserve">שעת סיום</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">לא חובה.</t>
+          <t xml:space="preserve">שעה בצורה 09:45. חייבת להיות אחרי שעת ההתחלה.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">תיאור</t>
+          <t xml:space="preserve">כותרת משנה</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">לא חובה. הטקסט שמופיע בעמוד הפעילות.</t>
+          <t xml:space="preserve">לא חובה.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">מיקום / קומה</t>
+          <t xml:space="preserve">כותרת משנה באנגלית</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">לא חובה. אולם, חדר או קומה.</t>
+          <t xml:space="preserve">לא חובה.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">מסלול</t>
+          <t xml:space="preserve">תיאור</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">לא חובה. מסלול תוכן.</t>
+          <t xml:space="preserve">לא חובה. הטקסט שמופיע בעמוד הפעילות.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">שפה</t>
+          <t xml:space="preserve">תיאור באנגלית</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">לא חובה. שפת הפעילות.</t>
+          <t xml:space="preserve">לא חובה. תרגום התיאור.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">מקומות</t>
+          <t xml:space="preserve">מיקום / קומה</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">לא חובה. מספר מקומות — רק לסדנאות וסיורים.</t>
+          <t xml:space="preserve">לא חובה. אולם, חדר או קומה.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">רשימת המתנה</t>
+          <t xml:space="preserve">מסלול</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">כן / לא. ברירת מחדל: לא.</t>
+          <t xml:space="preserve">לא חובה. מסלול תוכן.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">מוצג בעמוד הבית</t>
+          <t xml:space="preserve">מסלול באנגלית</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">כן / לא. ברירת מחדל: לא.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t xml:space="preserve">לא חובה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">שפה</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">לא חובה. שפת הפעילות.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t xml:space="preserve">מקומות</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">לא חובה. מספר מקומות — רק לסדנאות וסיורים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">רשימת המתנה</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">כן / לא. ברירת מחדל: לא.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מוצג בעמוד הבית</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">כן / לא. ברירת מחדל: לא.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">שימו לב</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">שורות הדוגמה נועדו למחיקה. אפשר להוסיף עמודות משלכם — הן פשוט יתעלמו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנגלית</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">כל עמודה "באנגלית" היא רשות. עמודה שנשארת ריקה — האתר באנגלית יציג במקומה את העברית, כך שאפשר לתרגם רק את מה שחשוב.</t>
         </is>
       </c>
     </row>
